--- a/Week 4 CellChat/data/Research Output.xlsx
+++ b/Week 4 CellChat/data/Research Output.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://keckmedicine-my.sharepoint.com/personal/j_nelson_med_usc_edu/Documents/Nelson USC Lab/JWN Effort Sankey Project/Dataset/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uscedu-my.sharepoint.com/personal/jnelson4_usc_edu/Documents/Github/score/Week 4 CellChat/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="8_{1395474D-CEF1-4BD1-B105-EC6936A43958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F08E3352-1AEC-4379-A823-C0B8A182093E}"/>
+  <xr:revisionPtr revIDLastSave="154" documentId="8_{1395474D-CEF1-4BD1-B105-EC6936A43958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0DCEB60-06AB-4839-A594-8DCFDB94EA56}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61D75E46-8A91-4DC6-BDEF-0CB13C20059F}"/>
+    <workbookView minimized="1" xWindow="1080" yWindow="1035" windowWidth="9360" windowHeight="5040" xr2:uid="{61D75E46-8A91-4DC6-BDEF-0CB13C20059F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -171,18 +171,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -199,7 +193,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -748,7 +742,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="M8" t="s">
+      <c r="M8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="N8">
